--- a/research/traditional_assets/database/data/namibia/namibia_financial_svcs_non_bank_insurance.xlsx
+++ b/research/traditional_assets/database/data/namibia/namibia_financial_svcs_non_bank_insurance.xlsx
@@ -587,6 +587,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.0505</v>
+      </c>
+      <c r="E2">
+        <v>-0.0168</v>
+      </c>
       <c r="G2">
         <v>0</v>
       </c>
@@ -600,82 +606,85 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>24.8</v>
+        <v>19</v>
       </c>
       <c r="L2">
-        <v>0.4815533980582524</v>
+        <v>0.4203539823008849</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="N2">
-        <v>0</v>
+        <v>0.1387614678899083</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.6368421052631579</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>12.1</v>
       </c>
       <c r="Q2">
-        <v>0</v>
+        <v>0.1387614678899083</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.6368421052631579</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
+      <c r="T2">
+        <v>0</v>
+      </c>
       <c r="U2">
-        <v>6.35</v>
+        <v>17.2</v>
       </c>
       <c r="V2">
-        <v>0.1020900321543408</v>
+        <v>0.1972477064220183</v>
       </c>
       <c r="W2">
-        <v>0.2006472491909385</v>
+        <v>0.116779348494161</v>
       </c>
       <c r="X2">
-        <v>0.04460526190651261</v>
+        <v>0.08340470469613898</v>
       </c>
       <c r="Y2">
-        <v>0.1560419872844259</v>
+        <v>0.03337464379802206</v>
       </c>
       <c r="Z2">
-        <v>0.3635465198362276</v>
+        <v>0.1968641114982578</v>
       </c>
       <c r="AA2">
         <v>0</v>
       </c>
       <c r="AB2">
-        <v>0.03991720887642682</v>
+        <v>0.07976233026686104</v>
       </c>
       <c r="AC2">
-        <v>-0.03991720887642682</v>
+        <v>-0.07976233026686104</v>
       </c>
       <c r="AD2">
-        <v>90.7</v>
+        <v>136.6</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>90.7</v>
+        <v>136.6</v>
       </c>
       <c r="AG2">
-        <v>84.35000000000001</v>
+        <v>119.4</v>
       </c>
       <c r="AH2">
-        <v>0.5931981687377371</v>
+        <v>0.6103663985701518</v>
       </c>
       <c r="AI2">
-        <v>0.3286231884057971</v>
+        <v>0.445822454308094</v>
       </c>
       <c r="AJ2">
-        <v>0.5755714773114978</v>
+        <v>0.5779283639883833</v>
       </c>
       <c r="AK2">
-        <v>0.3128129056183942</v>
+        <v>0.4128630705394191</v>
       </c>
       <c r="AL2">
         <v>0</v>
@@ -700,6 +709,12 @@
           <t>Financial Svcs. (Non-bank &amp; Insurance)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.0505</v>
+      </c>
+      <c r="E3">
+        <v>-0.0168</v>
+      </c>
       <c r="G3">
         <v>0</v>
       </c>
@@ -713,82 +728,85 @@
         <v>0</v>
       </c>
       <c r="K3">
-        <v>24.8</v>
+        <v>19</v>
       </c>
       <c r="L3">
-        <v>0.4815533980582524</v>
+        <v>0.4203539823008849</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>12.1</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.1387614678899083</v>
       </c>
       <c r="O3">
-        <v>-0</v>
+        <v>0.6368421052631579</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>12.1</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.1387614678899083</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.6368421052631579</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
+      <c r="T3">
+        <v>0</v>
+      </c>
       <c r="U3">
-        <v>6.35</v>
+        <v>17.2</v>
       </c>
       <c r="V3">
-        <v>0.1020900321543408</v>
+        <v>0.1972477064220183</v>
       </c>
       <c r="W3">
-        <v>0.2006472491909385</v>
+        <v>0.116779348494161</v>
       </c>
       <c r="X3">
-        <v>0.04460526190651261</v>
+        <v>0.08340470469613898</v>
       </c>
       <c r="Y3">
-        <v>0.1560419872844259</v>
+        <v>0.03337464379802206</v>
       </c>
       <c r="Z3">
-        <v>0.3635465198362276</v>
+        <v>0.1968641114982578</v>
       </c>
       <c r="AA3">
         <v>0</v>
       </c>
       <c r="AB3">
-        <v>0.03991720887642682</v>
+        <v>0.07976233026686104</v>
       </c>
       <c r="AC3">
-        <v>-0.03991720887642682</v>
+        <v>-0.07976233026686104</v>
       </c>
       <c r="AD3">
-        <v>90.7</v>
+        <v>136.6</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>90.7</v>
+        <v>136.6</v>
       </c>
       <c r="AG3">
-        <v>84.35000000000001</v>
+        <v>119.4</v>
       </c>
       <c r="AH3">
-        <v>0.5931981687377371</v>
+        <v>0.6103663985701518</v>
       </c>
       <c r="AI3">
-        <v>0.3286231884057971</v>
+        <v>0.445822454308094</v>
       </c>
       <c r="AJ3">
-        <v>0.5755714773114978</v>
+        <v>0.5779283639883833</v>
       </c>
       <c r="AK3">
-        <v>0.3128129056183942</v>
+        <v>0.4128630705394191</v>
       </c>
       <c r="AL3">
         <v>0</v>
